--- a/seo-audit.xlsx
+++ b/seo-audit.xlsx
@@ -10,13 +10,15 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Page Audit" sheetId="2" r:id="rId2"/>
     <sheet name="Links" sheetId="3" r:id="rId3"/>
+    <sheet name="Orphan Pages" sheetId="4" r:id="rId4"/>
+    <sheet name="Schema Gaps" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="241">
   <si>
     <t>Metric</t>
   </si>
@@ -36,6 +38,9 @@
     <t>URL</t>
   </si>
   <si>
+    <t>SEO Score</t>
+  </si>
+  <si>
     <t>Status Code</t>
   </si>
   <si>
@@ -51,124 +56,691 @@
     <t>Issues</t>
   </si>
   <si>
-    <t>https://togrowmarketing.com</t>
-  </si>
-  <si>
-    <t>https://www.togrowmarketing.com/seo-vs-paid-ads-for-new-businesses/</t>
+    <t>https://www.togrowmarketing.com/understanding-cloud-computing-togrowmarketing/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/introduction-to-google-analytics-basics/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/preparing-your-website-for-googles-mobile-first-indexing/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/how-to-get-your-financial-services-content-indexed-by-ai-engines/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/whatsapp-marketing-2025/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/how-to-use-internal-linking-to-boost-seo/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/design-digital-business-catalogue/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/eal-estate-seo-strategy/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/real-estate-seo-how-agents-can-get-found-on-google/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/the-7-core-pillars-of-digital-marketing/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/whats-up-with-the-new-google-business-4/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/ai-tools-for-digital-marketers-2025/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/how-to-do-keyword-research-tools-tips-templates/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/optimax_testimony_category/seo/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/ppc-b2c-vs-b2b-india-2025/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/the-secret-to-great-blog-posts-that-get-found/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/how-ai-tools-are-transforming-digital-marketing-workflows/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/link-building-in-the-ai-era-strategies-that-still-work/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/how-to-fix-crawl-errors-in-google-search-console-togrowmarketing/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/how-to-build-a-good-seo-strategy-for-a-new-website/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/case-studies/on-page-optimization/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/teams/samantha-riley-4/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/what-are-lsi-keywords-and-how-do-they-improve-seo/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/how-to-improve-your-domain-authority/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/the-power-of-influencer-marketing-how-to-leverage-it-for-your-brand/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/team-categories/team/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/understanding-return-on-investment-roi-in-digital-media-marketing/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/privacy-policy/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/introduction-to-google-analytics-guide/</t>
   </si>
   <si>
     <t>https://www.togrowmarketing.com/info-box-1/</t>
   </si>
   <si>
-    <t>https://www.togrowmarketing.com/contact-info-box-1/</t>
-  </si>
-  <si>
-    <t>https://www.togrowmarketing.com/?page_id=3924</t>
-  </si>
-  <si>
-    <t>https://www.togrowmarketing.com/blog/</t>
-  </si>
-  <si>
-    <t>https://www.togrowmarketing.com/ethics-of-ai-in-marketing-what-marketers-should-know/</t>
-  </si>
-  <si>
-    <t>https://www.togrowmarketing.com/courses/</t>
-  </si>
-  <si>
-    <t>https://www.togrowmarketing.com/?page_id=3846</t>
-  </si>
-  <si>
-    <t>https://www.togrowmarketing.com/radius-button/</t>
+    <t>https://www.togrowmarketing.com/about-1/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/case-studies/technical-optimization/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/ultimate-guide-to-digital-marketing-campaigns/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/team-categories/team-new/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/new-newsletter/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/real-data-management-consulting-4/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/chrome-extensions-for-digital-marketers-2025/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/growth-hacking-with-user-generated-content-ugc-on-instagram-reels/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/services/content-marketing/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/faceted-navigation-seo-challenges-and-fixes/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/pricing-plan-3/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/title-subtitle-shortcode/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/core-web-vitals-what-they-are-and-how-to-optimize-for-them/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/preparing-your-content-for-the-future-of-voice-search/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/testimonial-1/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/top-10-evergreen-blog-post-ideas-that-drive-traffic-all-year-round/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/neuromarketing-in-the-digital-age-unlocking-the-power-of-psychology-to-boost-ad-conversions/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/how-mobile-first-design-helps-improve-your-websites-seo/</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/counter-2/</t>
+  </si>
+  <si>
+    <t>Understanding Cloud Computing - Togrowmarketing - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Introduction to Google Analytics and the Basics – Beginner’s Guide</t>
+  </si>
+  <si>
+    <t>Preparing Your Website for Google’s Mobile-First Indexing - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>How to Get Your Financial Services Content Indexed by AI Engines - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>WhatsApp Marketing 2025 | How Businesses Drive Sales via Chats</t>
+  </si>
+  <si>
+    <t>How to Use Internal Linking to Boost SEO - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Design a Business Catalogue-Digital Marketing- Togrowmarketing</t>
+  </si>
+  <si>
+    <t>Real Estate SEO: Rank Higher, Get Leads &amp; Deals - Togrowmarketing</t>
+  </si>
+  <si>
+    <t>Real Estate SEO: How Agents Can Get Found on Google - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>The 7 Core Pillars of Digital Marketing - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>New Google Business What's Up With - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>AI Tools Every Digital Marketer Should Master in 2025 - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>How to Do Keyword Research: Tools, Tips &amp; Templates - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>SEO Archives - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>PPC B2C vs B2B India | Winning Ad Strategies for 2025</t>
+  </si>
+  <si>
+    <t>The Secret to Great Blog Posts That Get Found - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>How AI Tools Are Transforming Digital Marketing Workflows - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Link Building in the AI Era - Togrowmarketing - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>How to Fix Crawl Errors in Google Search Console -togrowmarketing - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>How to Build a Good SEO Strategy for a New Website - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>On-page optimization - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Samantha Riley - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>What Are LSI Keywords and How Do They Improve SEO? - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>How to Improve Your Domain Authority - To Grow Marketing - Marketing Consultation and Agency</t>
   </si>
   <si>
     <t>Digital Marketing Consultation Agency &amp; Online SEO courses</t>
   </si>
   <si>
-    <t>SEO vs Paid Ads Which is Better for New Businesses | To Grow</t>
+    <t>The Power of Influencer Marketing: How to Leverage It for Your Brand - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Team Archives - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Understanding Return on Investment (ROI) in Digital Media Marketing - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Privacy Policy - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Introduction to Google Analytics – Guide to Key Features &amp; Setup</t>
   </si>
   <si>
     <t>Info Box 1 - To Grow Marketing - Marketing Consultation and Agency</t>
   </si>
   <si>
-    <t>Contact Info Box 1 - To Grow Marketing - Marketing Consultation and Agency</t>
-  </si>
-  <si>
-    <t>Page not found - To Grow Marketing - Marketing Consultation and Agency</t>
-  </si>
-  <si>
-    <t>Blog - To Grow Marketing - Marketing Consultation and Agency</t>
-  </si>
-  <si>
-    <t>Ethics of AI in Marketing: What Marketers Should Know</t>
-  </si>
-  <si>
-    <t>Courses - To Grow Marketing - Marketing Consultation and Agency</t>
-  </si>
-  <si>
-    <t>Radius Button - To Grow Marketing - Marketing Consultation and Agency</t>
+    <t>About Us - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Technical optimization - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Ultimate Guide to Digital Marketing Campaigns - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Team New Archives - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>new newsletter - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Real Data Consulting Data Management - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Top 10 Chrome Extensions Every Digital Marketer Must Use in 2025</t>
+  </si>
+  <si>
+    <t>Growth Hacking with User - Togrowmarketing - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Content Marketing - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Faceted Navigation &amp; SEO: Challenges and Fixes - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Pricing Plan 3 - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Title Subtitle Shortcode - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Core Web Vitals: What They Are and How to Optimize for Them - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Preparing Your Content for the Future of Voice Search - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Testimonial - 1 - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Top 10 Evergreen Blog Post Ideas That Drive Traffic All Year Round - Togrowmarketing - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Neuromarketing in the digital age - Togrowmarketing - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>How Mobile-First Design Helps Improve Your Website’s SEO - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Counter 2 - To Grow Marketing - Marketing Consultation and Agency</t>
+  </si>
+  <si>
+    <t>Learn what Google Analytics is, how it works, its key features, and important metrics. A simple beginner’s guide to setting up and using Google Analytics effectively.</t>
+  </si>
+  <si>
+    <t>Discover WhatsApp Marketing trends for 2025. Learn how businesses use WhatsApp for customer engagement, leads, and sales growth in India and beyond.</t>
+  </si>
+  <si>
+    <t>Learn how to design a professional, engaging digital business catalogue that boosts conversions, strengthens your brand, and supports your digital marketing strategy.</t>
+  </si>
+  <si>
+    <t>Learn how real estate SEO can boost your visibility, attract quality leads, and help you sell properties faster. Tips on keywords, local SEO, listings &amp; more!</t>
+  </si>
+  <si>
+    <t>Master AI tools like Jasper, SurferSEO, and Predis.ai to stay ahead in digital marketing in 2025. Boost content, SEO, emails &amp; more</t>
+  </si>
+  <si>
+    <t>Discover what makes PPC work for B2C vs B2B in India. Learn ad tactics, targeting tips, and platform choices for 2025 digital success!</t>
   </si>
   <si>
     <t>To Grow Marketing - Chennai based digital agency offering SEO, PPC, social media, content marketing &amp; consultation along with online courses. Book your free audit!</t>
   </si>
   <si>
-    <t>SEO (Search Engine Optimization) vs Paid Ads for new businesses discover the benefits, costs, organic traffic potential, and ROI to choose the best digital growth strategy.</t>
-  </si>
-  <si>
-    <t>AI drives efficiency, but ethical risks can hurt your brand. Read our guide on navigating data privacy, bias, and compliance in modern marketing.</t>
-  </si>
-  <si>
-    <t>SEO vs Paid Ads: Which Works Better for New Businesses?</t>
+    <t>Discover what Google Analytics is, how it works, and its key features. Learn to track visitors, analyze traffic sources, and set up goals to grow your website effectively</t>
+  </si>
+  <si>
+    <t>Boost your productivity and SEO performance with the top 10 Chrome extensions every digital marketer needs in 2025. From keyword tools to competitor tracking, discover game-changers now.</t>
+  </si>
+  <si>
+    <t>Understanding Cloud Computing – Togrowmarketing</t>
+  </si>
+  <si>
+    <t>How to Set Up Google Analytics for Your Website – Simple Guide</t>
+  </si>
+  <si>
+    <t>Preparing Your Website for Google’s Mobile-First Indexing</t>
+  </si>
+  <si>
+    <t>How to Get Your Financial Services Content Indexed by AI Engines</t>
+  </si>
+  <si>
+    <t>WhatsApp Marketing in 2025: How Businesses Are Turning Conversations Into Sales</t>
+  </si>
+  <si>
+    <t>How to Use Internal Linking to Boost SEO</t>
+  </si>
+  <si>
+    <t>How to Design a Business Catalogue for Customers in Digital Marketing</t>
+  </si>
+  <si>
+    <t>Real Estate SEO: How to Rank Higher and Sell Properties Faster!</t>
+  </si>
+  <si>
+    <t>Real Estate SEO: How Agents Can Get Found on Google</t>
+  </si>
+  <si>
+    <t>The 7 Core Pillars of Digital Marketing</t>
+  </si>
+  <si>
+    <t>New Google Business What’s Up With</t>
+  </si>
+  <si>
+    <t>AI Tools Every Digital Marketer Should Master in 2025</t>
+  </si>
+  <si>
+    <t>How to Do Keyword Research: Tools, Tips &amp; Templates</t>
+  </si>
+  <si>
+    <t>Testimonial Category:SEO</t>
+  </si>
+  <si>
+    <t>PPC for B2C vs B2B in India: What Works, What Fails in 2025?</t>
+  </si>
+  <si>
+    <t>The Secret to Great Blog Posts That Get Found</t>
+  </si>
+  <si>
+    <t>How AI Tools Are Transforming Digital Marketing Workflows</t>
+  </si>
+  <si>
+    <t>Link Building in the AI Era – Togrowmarketing</t>
+  </si>
+  <si>
+    <t>How to Fix Crawl Errors in Google Search Console -togrowmarketing</t>
+  </si>
+  <si>
+    <t>How to Build a Good SEO Strategy for a New Website</t>
+  </si>
+  <si>
+    <t>On-page optimization</t>
+  </si>
+  <si>
+    <t>Samantha Riley</t>
+  </si>
+  <si>
+    <t>What Are LSI Keywords and How Do They Improve SEO?</t>
+  </si>
+  <si>
+    <t>How to Improve Your Domain Authority</t>
+  </si>
+  <si>
+    <t>The Power of Influencer Marketing: How to Leverage It for Your Brand</t>
+  </si>
+  <si>
+    <t>Team Category:Team</t>
+  </si>
+  <si>
+    <t>Understanding Return on Investment (ROI) in Digital Media Marketing</t>
+  </si>
+  <si>
+    <t>Privacy Policy</t>
+  </si>
+  <si>
+    <t>Introduction to Google Analytics and the Basics of Google Analytics</t>
   </si>
   <si>
     <t>Info Box 1</t>
   </si>
   <si>
-    <t>Contact Info Box 1</t>
-  </si>
-  <si>
-    <t>Page not Found</t>
-  </si>
-  <si>
-    <t>Blog</t>
-  </si>
-  <si>
-    <t>Courses</t>
-  </si>
-  <si>
-    <t>Radius Button</t>
+    <t>About Us</t>
+  </si>
+  <si>
+    <t>Technical optimization</t>
+  </si>
+  <si>
+    <t>Ultimate Guide to Digital Marketing Campaigns</t>
+  </si>
+  <si>
+    <t>Team Category:Team New</t>
+  </si>
+  <si>
+    <t>new newsletter</t>
+  </si>
+  <si>
+    <t>Real Data Consulting Data Management</t>
+  </si>
+  <si>
+    <t>Growth Hacking with User – Togrowmarketing</t>
+  </si>
+  <si>
+    <t>Content Marketing</t>
+  </si>
+  <si>
+    <t>Faceted Navigation &amp; SEO: Challenges and Fixes</t>
+  </si>
+  <si>
+    <t>Pricing Plan 3</t>
+  </si>
+  <si>
+    <t>Title Subtitle Shortcode</t>
+  </si>
+  <si>
+    <t>Core Web Vitals: What They Are and How to Optimize for Them</t>
+  </si>
+  <si>
+    <t>Preparing Your Content for the Future of Voice Search</t>
+  </si>
+  <si>
+    <t>Testimonial – 1</t>
+  </si>
+  <si>
+    <t>Top 10 Evergreen Blog Post Ideas That Drive Traffic All Year Round – Togrowmarketing</t>
+  </si>
+  <si>
+    <t>Neuromarketing in the digital age – Togrowmarketing</t>
+  </si>
+  <si>
+    <t>How Mobile-First Design Helps Improve Your Website’s SEO</t>
+  </si>
+  <si>
+    <t>Counter 2</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (103 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (66 characters) | ⚠️ Meta description too long (166 characters)</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (113 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (120 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (62 characters)</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (96 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (62 characters) | ⚠️ Meta description too long (166 characters)</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (65 characters)</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (107 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (95 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (90 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (109 characters)</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (68 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>No issues</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (101 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (121 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (106 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (76 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (70 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (92 characters) | ❌ Missing meta description</t>
   </si>
   <si>
     <t>⚠️ Meta description too long (163 characters) | ❌ Missing H1 tag</t>
   </si>
   <si>
-    <t>⚠️ Meta description too long (172 characters)</t>
+    <t>⚠️ Title too long (124 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (69 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (123 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (64 characters) | ⚠️ Meta description too long (170 characters)</t>
   </si>
   <si>
     <t>⚠️ Title too long (66 characters) | ❌ Missing meta description</t>
   </si>
   <si>
-    <t>⚠️ Title too long (74 characters) | ❌ Missing meta description</t>
-  </si>
-  <si>
-    <t>⚠️ Title too long (70 characters) | ❌ Missing meta description</t>
-  </si>
-  <si>
-    <t>❌ Missing meta description</t>
-  </si>
-  <si>
-    <t>No issues</t>
-  </si>
-  <si>
-    <t>⚠️ Title too long (63 characters) | ❌ Missing meta description</t>
-  </si>
-  <si>
-    <t>⚠️ Title too long (69 characters) | ❌ Missing meta description</t>
+    <t>⚠️ Title too long (64 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (78 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (73 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (64 characters) | ⚠️ Meta description too long (186 characters)</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (98 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (102 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (80 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (115 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (109 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (71 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (140 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (112 characters) | ❌ Missing meta description</t>
+  </si>
+  <si>
+    <t>⚠️ Title too long (65 characters) | ❌ Missing meta description</t>
   </si>
   <si>
     <t>Internal Links</t>
   </si>
   <si>
     <t>External Links</t>
+  </si>
+  <si>
+    <t>Orphan URL</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/chrome-extensions-for-digital-marketers-2025</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/core-web-vitals-what-they-are-and-how-to-optimize-for-them</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/counter-2</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/design-digital-business-catalogue</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/faceted-navigation-seo-challenges-and-fixes</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/how-to-build-a-good-seo-strategy-for-a-new-website</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/how-to-do-keyword-research-tools-tips-templates</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/how-to-fix-crawl-errors-in-google-search-console-togrowmarketing</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/link-building-in-the-ai-era-strategies-that-still-work</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/neuromarketing-in-the-digital-age-unlocking-the-power-of-psychology-to-boost-ad-conversions</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/new-newsletter</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/optimax_testimony_category/seo</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/privacy-policy</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/team-categories/team</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/the-7-core-pillars-of-digital-marketing</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/the-power-of-influencer-marketing-how-to-leverage-it-for-your-brand</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/title-subtitle-shortcode</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/top-10-evergreen-blog-post-ideas-that-drive-traffic-all-year-round</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/understanding-cloud-computing-togrowmarketing</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/understanding-return-on-investment-roi-in-digital-media-marketing</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/what-are-lsi-keywords-and-how-do-they-improve-seo</t>
+  </si>
+  <si>
+    <t>https://www.togrowmarketing.com/whatsapp-marketing-2025</t>
+  </si>
+  <si>
+    <t>Expected Schema</t>
+  </si>
+  <si>
+    <t>Found Schemas</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>Person</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>ReadAction, BreadcrumbList, PropertyValueSpecification, ListItem, Article, Person, WebPage, WebSite, Organization, SearchAction, EntryPoint, ImageObject, CommentAction</t>
+  </si>
+  <si>
+    <t>ReadAction, PropertyValueSpecification, ListItem, WebPage, WebSite, Organization, SearchAction, EntryPoint, BreadcrumbList, ImageObject</t>
+  </si>
+  <si>
+    <t>PropertyValueSpecification, ListItem, WebSite, Organization, CollectionPage, SearchAction, EntryPoint, BreadcrumbList, ImageObject</t>
   </si>
 </sst>
 </file>
@@ -555,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -571,7 +1143,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -581,10 +1153,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -603,181 +1175,1032 @@
       <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
-        <v>200</v>
-      </c>
-      <c r="C2" t="s">
+        <v>67.5</v>
+      </c>
+      <c r="C2">
+        <v>200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>85.5</v>
+      </c>
+      <c r="C3">
+        <v>200</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>90</v>
+      </c>
+      <c r="C4">
+        <v>200</v>
+      </c>
+      <c r="D4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>90</v>
+      </c>
+      <c r="C5">
+        <v>200</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>67.5</v>
+      </c>
+      <c r="C6">
+        <v>200</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>90</v>
+      </c>
+      <c r="C7">
+        <v>200</v>
+      </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>63</v>
+      </c>
+      <c r="C8">
+        <v>200</v>
+      </c>
+      <c r="D8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>90</v>
+      </c>
+      <c r="C9">
+        <v>200</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>90</v>
+      </c>
+      <c r="C10">
+        <v>200</v>
+      </c>
+      <c r="D10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B11">
+        <v>67.5</v>
+      </c>
+      <c r="C11">
+        <v>200</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12">
+        <v>90</v>
+      </c>
+      <c r="C12">
+        <v>200</v>
+      </c>
+      <c r="D12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13">
+        <v>90</v>
+      </c>
+      <c r="C13">
+        <v>200</v>
+      </c>
+      <c r="D13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14">
+        <v>67.5</v>
+      </c>
+      <c r="C14">
+        <v>200</v>
+      </c>
+      <c r="D14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15">
+        <v>67.5</v>
+      </c>
+      <c r="C15">
+        <v>200</v>
+      </c>
+      <c r="D15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <v>97.2</v>
+      </c>
+      <c r="C16">
+        <v>200</v>
+      </c>
+      <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" t="s">
+        <v>135</v>
+      </c>
+      <c r="G16" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17">
+        <v>90</v>
+      </c>
+      <c r="C17">
+        <v>200</v>
+      </c>
+      <c r="D17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18">
+        <v>90</v>
+      </c>
+      <c r="C18">
+        <v>200</v>
+      </c>
+      <c r="D18" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" t="s">
+        <v>137</v>
+      </c>
+      <c r="G18" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19">
+        <v>67.5</v>
+      </c>
+      <c r="C19">
+        <v>200</v>
+      </c>
+      <c r="D19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B20">
+        <v>67.5</v>
+      </c>
+      <c r="C20">
+        <v>200</v>
+      </c>
+      <c r="D20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21">
+        <v>67.5</v>
+      </c>
+      <c r="C21">
+        <v>200</v>
+      </c>
+      <c r="D21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22">
+        <v>90</v>
+      </c>
+      <c r="C22">
+        <v>200</v>
+      </c>
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" t="s">
+        <v>141</v>
+      </c>
+      <c r="G22" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23">
+        <v>90</v>
+      </c>
+      <c r="C23">
+        <v>200</v>
+      </c>
+      <c r="D23" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24">
+        <v>67.5</v>
+      </c>
+      <c r="C24">
+        <v>200</v>
+      </c>
+      <c r="D24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24" t="s">
+        <v>143</v>
+      </c>
+      <c r="G24" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25">
+        <v>90</v>
+      </c>
+      <c r="C25">
+        <v>200</v>
+      </c>
+      <c r="D25" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" t="s">
+        <v>144</v>
+      </c>
+      <c r="G25" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>74.7</v>
+      </c>
+      <c r="C26">
+        <v>200</v>
+      </c>
+      <c r="D26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27">
+        <v>67.5</v>
+      </c>
+      <c r="C27">
+        <v>200</v>
+      </c>
+      <c r="D27" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27" t="s">
+        <v>145</v>
+      </c>
+      <c r="G27" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28">
+        <v>67.5</v>
+      </c>
+      <c r="C28">
+        <v>200</v>
+      </c>
+      <c r="D28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F28" t="s">
+        <v>146</v>
+      </c>
+      <c r="G28" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29">
+        <v>67.5</v>
+      </c>
+      <c r="C29">
+        <v>200</v>
+      </c>
+      <c r="D29" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29" t="s">
+        <v>147</v>
+      </c>
+      <c r="G29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3">
-        <v>200</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="B30">
+        <v>67.5</v>
+      </c>
+      <c r="C30">
+        <v>200</v>
+      </c>
+      <c r="D30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" t="s">
+        <v>148</v>
+      </c>
+      <c r="G30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4">
-        <v>200</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="B31">
+        <v>85.5</v>
+      </c>
+      <c r="C31">
+        <v>200</v>
+      </c>
+      <c r="D31" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" t="s">
+        <v>149</v>
+      </c>
+      <c r="G31" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
-        <v>200</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="B32">
+        <v>90</v>
+      </c>
+      <c r="C32">
+        <v>200</v>
+      </c>
+      <c r="D32" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" t="s">
+        <v>150</v>
+      </c>
+      <c r="G32" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6">
-        <v>404</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="B33">
+        <v>90</v>
+      </c>
+      <c r="C33">
+        <v>200</v>
+      </c>
+      <c r="D33" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" t="s">
+        <v>151</v>
+      </c>
+      <c r="G33" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>200</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="B34">
+        <v>90</v>
+      </c>
+      <c r="C34">
+        <v>200</v>
+      </c>
+      <c r="D34" t="s">
+        <v>94</v>
+      </c>
+      <c r="F34" t="s">
+        <v>152</v>
+      </c>
+      <c r="G34" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
-        <v>200</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="B35">
+        <v>90</v>
+      </c>
+      <c r="C35">
+        <v>200</v>
+      </c>
+      <c r="D35" t="s">
+        <v>95</v>
+      </c>
+      <c r="F35" t="s">
+        <v>153</v>
+      </c>
+      <c r="G35" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9">
-        <v>200</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="B36">
+        <v>90</v>
+      </c>
+      <c r="C36">
+        <v>200</v>
+      </c>
+      <c r="D36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" t="s">
+        <v>154</v>
+      </c>
+      <c r="G36" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10">
-        <v>404</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11">
-        <v>200</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="B37">
+        <v>67.5</v>
+      </c>
+      <c r="C37">
+        <v>200</v>
+      </c>
+      <c r="D37" t="s">
+        <v>97</v>
+      </c>
+      <c r="F37" t="s">
+        <v>155</v>
+      </c>
+      <c r="G37" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="2" t="s">
         <v>48</v>
+      </c>
+      <c r="B38">
+        <v>90</v>
+      </c>
+      <c r="C38">
+        <v>200</v>
+      </c>
+      <c r="D38" t="s">
+        <v>98</v>
+      </c>
+      <c r="F38" t="s">
+        <v>156</v>
+      </c>
+      <c r="G38" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39">
+        <v>63</v>
+      </c>
+      <c r="C39">
+        <v>200</v>
+      </c>
+      <c r="D39" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" t="s">
+        <v>120</v>
+      </c>
+      <c r="F39" t="s">
+        <v>99</v>
+      </c>
+      <c r="G39" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40">
+        <v>90</v>
+      </c>
+      <c r="C40">
+        <v>200</v>
+      </c>
+      <c r="D40" t="s">
+        <v>100</v>
+      </c>
+      <c r="F40" t="s">
+        <v>157</v>
+      </c>
+      <c r="G40" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41">
+        <v>100</v>
+      </c>
+      <c r="C41">
+        <v>200</v>
+      </c>
+      <c r="D41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
+        <v>158</v>
+      </c>
+      <c r="G41" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42">
+        <v>67.5</v>
+      </c>
+      <c r="C42">
+        <v>200</v>
+      </c>
+      <c r="D42" t="s">
+        <v>102</v>
+      </c>
+      <c r="F42" t="s">
+        <v>159</v>
+      </c>
+      <c r="G42" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43">
+        <v>90</v>
+      </c>
+      <c r="C43">
+        <v>200</v>
+      </c>
+      <c r="D43" t="s">
+        <v>103</v>
+      </c>
+      <c r="F43" t="s">
+        <v>160</v>
+      </c>
+      <c r="G43" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44">
+        <v>67.5</v>
+      </c>
+      <c r="C44">
+        <v>200</v>
+      </c>
+      <c r="D44" t="s">
+        <v>104</v>
+      </c>
+      <c r="F44" t="s">
+        <v>161</v>
+      </c>
+      <c r="G44" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45">
+        <v>67.5</v>
+      </c>
+      <c r="C45">
+        <v>200</v>
+      </c>
+      <c r="D45" t="s">
+        <v>105</v>
+      </c>
+      <c r="F45" t="s">
+        <v>162</v>
+      </c>
+      <c r="G45" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46">
+        <v>90</v>
+      </c>
+      <c r="C46">
+        <v>200</v>
+      </c>
+      <c r="D46" t="s">
+        <v>106</v>
+      </c>
+      <c r="F46" t="s">
+        <v>163</v>
+      </c>
+      <c r="G46" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47">
+        <v>90</v>
+      </c>
+      <c r="C47">
+        <v>200</v>
+      </c>
+      <c r="D47" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" t="s">
+        <v>164</v>
+      </c>
+      <c r="G47" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48">
+        <v>67.5</v>
+      </c>
+      <c r="C48">
+        <v>200</v>
+      </c>
+      <c r="D48" t="s">
+        <v>108</v>
+      </c>
+      <c r="F48" t="s">
+        <v>165</v>
+      </c>
+      <c r="G48" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49">
+        <v>67.5</v>
+      </c>
+      <c r="C49">
+        <v>200</v>
+      </c>
+      <c r="D49" t="s">
+        <v>109</v>
+      </c>
+      <c r="F49" t="s">
+        <v>166</v>
+      </c>
+      <c r="G49" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50">
+        <v>90</v>
+      </c>
+      <c r="C50">
+        <v>200</v>
+      </c>
+      <c r="D50" t="s">
+        <v>110</v>
+      </c>
+      <c r="F50" t="s">
+        <v>167</v>
+      </c>
+      <c r="G50" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51">
+        <v>67.5</v>
+      </c>
+      <c r="C51">
+        <v>200</v>
+      </c>
+      <c r="D51" t="s">
+        <v>111</v>
+      </c>
+      <c r="F51" t="s">
+        <v>168</v>
+      </c>
+      <c r="G51" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -792,6 +2215,46 @@
     <hyperlink ref="A9" r:id="rId8"/>
     <hyperlink ref="A10" r:id="rId9"/>
     <hyperlink ref="A11" r:id="rId10"/>
+    <hyperlink ref="A12" r:id="rId11"/>
+    <hyperlink ref="A13" r:id="rId12"/>
+    <hyperlink ref="A14" r:id="rId13"/>
+    <hyperlink ref="A15" r:id="rId14"/>
+    <hyperlink ref="A16" r:id="rId15"/>
+    <hyperlink ref="A17" r:id="rId16"/>
+    <hyperlink ref="A18" r:id="rId17"/>
+    <hyperlink ref="A19" r:id="rId18"/>
+    <hyperlink ref="A20" r:id="rId19"/>
+    <hyperlink ref="A21" r:id="rId20"/>
+    <hyperlink ref="A22" r:id="rId21"/>
+    <hyperlink ref="A23" r:id="rId22"/>
+    <hyperlink ref="A24" r:id="rId23"/>
+    <hyperlink ref="A25" r:id="rId24"/>
+    <hyperlink ref="A26" r:id="rId25"/>
+    <hyperlink ref="A27" r:id="rId26"/>
+    <hyperlink ref="A28" r:id="rId27"/>
+    <hyperlink ref="A29" r:id="rId28"/>
+    <hyperlink ref="A30" r:id="rId29"/>
+    <hyperlink ref="A31" r:id="rId30"/>
+    <hyperlink ref="A32" r:id="rId31"/>
+    <hyperlink ref="A33" r:id="rId32"/>
+    <hyperlink ref="A34" r:id="rId33"/>
+    <hyperlink ref="A35" r:id="rId34"/>
+    <hyperlink ref="A36" r:id="rId35"/>
+    <hyperlink ref="A37" r:id="rId36"/>
+    <hyperlink ref="A38" r:id="rId37"/>
+    <hyperlink ref="A39" r:id="rId38"/>
+    <hyperlink ref="A40" r:id="rId39"/>
+    <hyperlink ref="A41" r:id="rId40"/>
+    <hyperlink ref="A42" r:id="rId41"/>
+    <hyperlink ref="A43" r:id="rId42"/>
+    <hyperlink ref="A44" r:id="rId43"/>
+    <hyperlink ref="A45" r:id="rId44"/>
+    <hyperlink ref="A46" r:id="rId45"/>
+    <hyperlink ref="A47" r:id="rId46"/>
+    <hyperlink ref="A48" r:id="rId47"/>
+    <hyperlink ref="A49" r:id="rId48"/>
+    <hyperlink ref="A50" r:id="rId49"/>
+    <hyperlink ref="A51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -799,7 +2262,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -807,29 +2270,29 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -837,54 +2300,54 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
-        <v>61</v>
+        <v>139</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C8">
         <v>9</v>
@@ -892,34 +2355,474 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
+        <v>133</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12">
+        <v>133</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13">
+        <v>136</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14">
+        <v>133</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15">
+        <v>135</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <v>133</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17">
+        <v>133</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18">
+        <v>131</v>
+      </c>
+      <c r="C18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19">
+        <v>133</v>
+      </c>
+      <c r="C19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20">
+        <v>133</v>
+      </c>
+      <c r="C20">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21">
+        <v>133</v>
+      </c>
+      <c r="C21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22">
+        <v>65</v>
+      </c>
+      <c r="C22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23">
+        <v>64</v>
+      </c>
+      <c r="C23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24">
+        <v>133</v>
+      </c>
+      <c r="C24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25">
+        <v>133</v>
+      </c>
+      <c r="C25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>67</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27">
+        <v>134</v>
+      </c>
+      <c r="C27">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28">
+        <v>62</v>
+      </c>
+      <c r="C28">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29">
+        <v>136</v>
+      </c>
+      <c r="C29">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30">
         <v>61</v>
       </c>
-      <c r="C11">
+      <c r="C30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31">
+        <v>133</v>
+      </c>
+      <c r="C31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32">
+        <v>61</v>
+      </c>
+      <c r="C32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33">
+        <v>61</v>
+      </c>
+      <c r="C33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34">
+        <v>64</v>
+      </c>
+      <c r="C34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35">
+        <v>137</v>
+      </c>
+      <c r="C35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36">
+        <v>63</v>
+      </c>
+      <c r="C36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37">
+        <v>61</v>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38">
+        <v>133</v>
+      </c>
+      <c r="C38">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39">
+        <v>133</v>
+      </c>
+      <c r="C39">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40">
+        <v>133</v>
+      </c>
+      <c r="C40">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41">
+        <v>66</v>
+      </c>
+      <c r="C41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42">
+        <v>133</v>
+      </c>
+      <c r="C42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43">
+        <v>61</v>
+      </c>
+      <c r="C43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44">
+        <v>61</v>
+      </c>
+      <c r="C44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45">
+        <v>133</v>
+      </c>
+      <c r="C45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46">
+        <v>133</v>
+      </c>
+      <c r="C46">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47">
+        <v>61</v>
+      </c>
+      <c r="C47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48">
+        <v>133</v>
+      </c>
+      <c r="C48">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49">
+        <v>133</v>
+      </c>
+      <c r="C49">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50">
+        <v>133</v>
+      </c>
+      <c r="C50">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51">
+        <v>61</v>
+      </c>
+      <c r="C51">
         <v>5</v>
       </c>
     </row>
@@ -935,6 +2838,302 @@
     <hyperlink ref="A9" r:id="rId8"/>
     <hyperlink ref="A10" r:id="rId9"/>
     <hyperlink ref="A11" r:id="rId10"/>
+    <hyperlink ref="A12" r:id="rId11"/>
+    <hyperlink ref="A13" r:id="rId12"/>
+    <hyperlink ref="A14" r:id="rId13"/>
+    <hyperlink ref="A15" r:id="rId14"/>
+    <hyperlink ref="A16" r:id="rId15"/>
+    <hyperlink ref="A17" r:id="rId16"/>
+    <hyperlink ref="A18" r:id="rId17"/>
+    <hyperlink ref="A19" r:id="rId18"/>
+    <hyperlink ref="A20" r:id="rId19"/>
+    <hyperlink ref="A21" r:id="rId20"/>
+    <hyperlink ref="A22" r:id="rId21"/>
+    <hyperlink ref="A23" r:id="rId22"/>
+    <hyperlink ref="A24" r:id="rId23"/>
+    <hyperlink ref="A25" r:id="rId24"/>
+    <hyperlink ref="A26" r:id="rId25"/>
+    <hyperlink ref="A27" r:id="rId26"/>
+    <hyperlink ref="A28" r:id="rId27"/>
+    <hyperlink ref="A29" r:id="rId28"/>
+    <hyperlink ref="A30" r:id="rId29"/>
+    <hyperlink ref="A31" r:id="rId30"/>
+    <hyperlink ref="A32" r:id="rId31"/>
+    <hyperlink ref="A33" r:id="rId32"/>
+    <hyperlink ref="A34" r:id="rId33"/>
+    <hyperlink ref="A35" r:id="rId34"/>
+    <hyperlink ref="A36" r:id="rId35"/>
+    <hyperlink ref="A37" r:id="rId36"/>
+    <hyperlink ref="A38" r:id="rId37"/>
+    <hyperlink ref="A39" r:id="rId38"/>
+    <hyperlink ref="A40" r:id="rId39"/>
+    <hyperlink ref="A41" r:id="rId40"/>
+    <hyperlink ref="A42" r:id="rId41"/>
+    <hyperlink ref="A43" r:id="rId42"/>
+    <hyperlink ref="A44" r:id="rId43"/>
+    <hyperlink ref="A45" r:id="rId44"/>
+    <hyperlink ref="A46" r:id="rId45"/>
+    <hyperlink ref="A47" r:id="rId46"/>
+    <hyperlink ref="A48" r:id="rId47"/>
+    <hyperlink ref="A49" r:id="rId48"/>
+    <hyperlink ref="A50" r:id="rId49"/>
+    <hyperlink ref="A51" r:id="rId50"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="A5" r:id="rId4"/>
+    <hyperlink ref="A6" r:id="rId5"/>
+    <hyperlink ref="A7" r:id="rId6"/>
+    <hyperlink ref="A8" r:id="rId7"/>
+    <hyperlink ref="A9" r:id="rId8"/>
+    <hyperlink ref="A10" r:id="rId9"/>
+    <hyperlink ref="A11" r:id="rId10"/>
+    <hyperlink ref="A12" r:id="rId11"/>
+    <hyperlink ref="A13" r:id="rId12"/>
+    <hyperlink ref="A14" r:id="rId13"/>
+    <hyperlink ref="A15" r:id="rId14"/>
+    <hyperlink ref="A16" r:id="rId15"/>
+    <hyperlink ref="A17" r:id="rId16"/>
+    <hyperlink ref="A18" r:id="rId17"/>
+    <hyperlink ref="A19" r:id="rId18"/>
+    <hyperlink ref="A20" r:id="rId19"/>
+    <hyperlink ref="A21" r:id="rId20"/>
+    <hyperlink ref="A22" r:id="rId21"/>
+    <hyperlink ref="A23" r:id="rId22"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="A5" r:id="rId4"/>
+    <hyperlink ref="A6" r:id="rId5"/>
+    <hyperlink ref="A7" r:id="rId6"/>
+    <hyperlink ref="A8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
